--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127129026</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127128987</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127129026</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127128987</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127129026</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127128987</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127129026</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127128987</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127129026</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127128987</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98501</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127129026</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127129009</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127128987</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127129100</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127129026</v>
+        <v>127129009</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596491</v>
+        <v>596526</v>
       </c>
       <c r="R2" t="n">
-        <v>6985661</v>
+        <v>6985682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127129009</v>
+        <v>127128987</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596526</v>
+        <v>596549</v>
       </c>
       <c r="R3" t="n">
-        <v>6985682</v>
+        <v>6985713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128987</v>
+        <v>127129026</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596549</v>
+        <v>596491</v>
       </c>
       <c r="R4" t="n">
-        <v>6985713</v>
+        <v>6985661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>127129319</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,45 +1093,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127129100</v>
+        <v>127129460</v>
       </c>
       <c r="B6" t="n">
-        <v>98501</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596448</v>
+        <v>596559</v>
       </c>
       <c r="R6" t="n">
-        <v>6985613</v>
+        <v>6985775</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1171,11 @@
           <t>2025-08-03</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1187,6 +1197,205 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127134153</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596565</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6985774</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127129100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6985613</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22571-2025 artfynd.xlsx
+++ b/artfynd/A 22571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129009</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129319</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129460</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127134153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,8 +1431,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>